--- a/output/pdf_financials_xlsx/RAMM.xlsx
+++ b/output/pdf_financials_xlsx/RAMM.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.195544</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.033612</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006593</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.661311</v>
+        <v>-7.856855</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-16.46664</v>
+        <v>-16.500252</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.894798</v>
+        <v>-8.901391</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.661311</v>
+        <v>-7.856855</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-16.46664</v>
+        <v>-16.500252</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.894798</v>
+        <v>-8.901391</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-151.252018158192</v>
+        <v>-155.112509481247</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-379.2429990400684</v>
+        <v>-380.0171166307691</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-264.675874045345</v>
+        <v>-264.8720570320278</v>
       </c>
     </row>
     <row r="31">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">

--- a/output/pdf_financials_xlsx/RAMM.xlsx
+++ b/output/pdf_financials_xlsx/RAMM.xlsx
@@ -2227,13 +2227,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.152166</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1.215643</v>
       </c>
     </row>
     <row r="113">
@@ -4570,7 +4570,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.152166</v>
       </c>

--- a/output/pdf_financials_xlsx/RAMM.xlsx
+++ b/output/pdf_financials_xlsx/RAMM.xlsx
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>1.337052</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>1.206522</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.734764</v>
       </c>
     </row>
     <row r="29">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.856855</v>
+        <v>-6.519803</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-16.500252</v>
+        <v>-15.29373</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.901391</v>
+        <v>-8.166627</v>
       </c>
     </row>
     <row r="30">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-155.112509481247</v>
+        <v>-128.7160071877822</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-380.0171166307691</v>
+        <v>-352.229722135728</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-264.8720570320278</v>
+        <v>-243.0082323654021</v>
       </c>
     </row>
     <row r="31">
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.560642</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.391406</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.242707</v>
       </c>
     </row>
     <row r="41">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>2.329164</v>
+        <v>2.889806</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.996353</v>
+        <v>2.387759</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.907592</v>
+        <v>1.150299</v>
       </c>
     </row>
     <row r="42">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.006911</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.006983</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.22538</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.103483</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.068962</v>
       </c>
     </row>
     <row r="71">
@@ -1580,13 +1580,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.22538</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.103483</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.068962</v>
       </c>
     </row>
     <row r="72">
@@ -1644,13 +1644,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.232291</v>
+        <v>0.006911</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.111505</v>
+        <v>0.008022</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.068962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>0.006100821574590282</v>
+        <v>0.01374992686209116</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.006221262068519398</v>
+        <v>0.01381085562045622</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.002006293006878994</v>
+        <v>0.01410898530397392</v>
       </c>
     </row>
     <row r="81">
@@ -2035,13 +2035,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.337052</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.206522</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.734764</v>
       </c>
     </row>
     <row r="101">
@@ -3098,7 +3098,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3849,7 +3853,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.22538</v>
       </c>
@@ -4073,7 +4081,11 @@
           <t>Depreciation and amortization expense</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>1.337052</v>
       </c>
